--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.341549120226056</v>
+        <v>1.193001732036734</v>
       </c>
       <c r="D2" t="n">
-        <v>7.535789945298913</v>
+        <v>1.224565866111073</v>
       </c>
       <c r="E2" t="n">
-        <v>17.77797941219383</v>
+        <v>2.888921654481497</v>
       </c>
       <c r="F2" t="n">
-        <v>17.64317441775649</v>
+        <v>2.867015842885429</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.89750794461371</v>
+        <v>6.970845040999729</v>
       </c>
       <c r="D3" t="n">
-        <v>42.82213878081188</v>
+        <v>6.958597551881931</v>
       </c>
       <c r="E3" t="n">
-        <v>17.77797941219383</v>
+        <v>2.888921654481497</v>
       </c>
       <c r="F3" t="n">
-        <v>17.64317441775649</v>
+        <v>2.867015842885429</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
